--- a/data/trans_orig/IP29_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>36960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>68605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82671</t>
+          <t>82668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48581</t>
+          <t>47587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64244</t>
+          <t>63886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79016</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83615</t>
+          <t>83582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137172</t>
+          <t>138574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158511</t>
+          <t>159505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>30156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>42832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60591</t>
+          <t>60870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33064</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69633</t>
+          <t>69354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>87392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49966</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48141</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59849</t>
+          <t>59549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>49079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61794</t>
+          <t>61712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118975</t>
+          <t>119464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42163</t>
+          <t>42122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66381</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>77351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55571</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43028</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72816</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53894</t>
+          <t>54467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87990</t>
+          <t>88125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112902</t>
+          <t>112320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>59294</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77287</t>
+          <t>77581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71985</t>
+          <t>71412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>89944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136791</t>
+          <t>137373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161703</t>
+          <t>161568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>53450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77950</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>114021</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129711</t>
+          <t>129697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113258</t>
+          <t>113566</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130536</t>
+          <t>130665</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>233124</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255085</t>
+          <t>256772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>187669</t>
+          <t>186301</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>226564</t>
+          <t>225741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>180081</t>
+          <t>180744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218392</t>
+          <t>218650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>379329</t>
+          <t>379490</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>433388</t>
+          <t>432192</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>426201</t>
+          <t>427024</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>465096</t>
+          <t>466464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>477045</t>
+          <t>476787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>515356</t>
+          <t>514693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>914814</t>
+          <t>916010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>968873</t>
+          <t>968712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34716</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27748</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>59016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33636</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34336</t>
+          <t>34925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76955</t>
+          <t>76642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>33390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65869</t>
+          <t>66537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>81841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74252</t>
+          <t>75152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89370</t>
+          <t>88991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144877</t>
+          <t>145129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166351</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50196</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60430</t>
+          <t>60439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60727</t>
+          <t>60611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103783</t>
+          <t>103707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117963</t>
+          <t>118282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>36403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>30605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42635</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>62922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41388</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54351</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>63499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95296</t>
+          <t>94752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115039</t>
+          <t>113641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>23762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30594</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>62511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>75015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46672</t>
+          <t>46570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79065</t>
+          <t>80421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94568</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37701</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38739</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98804</t>
+          <t>98397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115104</t>
+          <t>114952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103667</t>
+          <t>102746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120590</t>
+          <t>119646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208000</t>
+          <t>207987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230019</t>
+          <t>231206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>52522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,82 +6471,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>38005</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>29361</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>47018</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>80291</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>69022</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>94679</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>21,08%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>38005</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>29035</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>46898</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>80291</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>68339</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>93239</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108792</t>
+          <t>107711</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>126063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,82 +6584,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>129126</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>120113</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>137770</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>77,26%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>71,87%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>82,43%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>247073</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>232685</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>258342</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>71,08%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>78,92%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>129126</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>120233</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>138096</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>77,26%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>71,94%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>82,63%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>247073</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>234125</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>259025</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207315</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>155443</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>194490</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>337279</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>392290</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>487886</t>
+          <t>488110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>525055</t>
+          <t>527491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>538899</t>
+          <t>539804</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>577652</t>
+          <t>577946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1036301</t>
+          <t>1039680</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1093714</t>
+          <t>1091312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40530</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77343</t>
+          <t>77322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>37487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71629</t>
+          <t>70105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83960</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91395</t>
+          <t>91282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152814</t>
+          <t>153600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172411</t>
+          <t>172205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37701</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>46339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65396</t>
+          <t>64619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>32712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>45550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67779</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86040</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>43425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63611</t>
+          <t>62572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84221</t>
+          <t>83105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>29668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>70975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>91508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35247</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74363</t>
+          <t>74535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83100</t>
+          <t>83135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53005</t>
+          <t>53256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41349</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57546</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74928</t>
+          <t>75145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28452</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45255</t>
+          <t>44389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57552</t>
+          <t>57081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80404</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107126</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94811</t>
+          <t>95677</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111614</t>
+          <t>111802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192342</t>
+          <t>191322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215194</t>
+          <t>215665</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41006</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30957</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83307</t>
+          <t>84815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119449</t>
+          <t>118434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135278</t>
+          <t>135399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115846</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134506</t>
+          <t>134065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>242612</t>
+          <t>241104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264399</t>
+          <t>266404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181116</t>
+          <t>181939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>217984</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>198247</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>240145</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,47 +10172,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>390945</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>448340</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>27,66%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>420535</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>391273</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>448977</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>468355</t>
+          <t>467556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>505223</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>486306</t>
+          <t>487000</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>525983</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,47 +10285,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>992949</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>965144</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1022539</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>72,34%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>992949</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>964507</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1022211</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
         </is>
       </c>
     </row>
